--- a/Portfolio_Tracker_Kenya.xlsx
+++ b/Portfolio_Tracker_Kenya.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c1e174b27b94807/Desktop/PortfolioTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_09C9AF2A7231FE99B5EDE0B00038F1AF6A203683" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E2327BA-9466-4EBF-B5A5-66E5D170D2F5}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_09C9AF2A7231FE99B5EDE0B00038F1AF6A203683" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0A67AFC-FFFA-470D-8C95-E63111FAD9FE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1043,16 +1043,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>33.161840930597691</c:v>
+                  <c:v>32.892193364440118</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.572087410384142</c:v>
+                  <c:v>17.097067097143984</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>23.988044691002454</c:v>
+                  <c:v>22.082881721849194</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.278026968015713</c:v>
+                  <c:v>27.927857816566704</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,16 +1307,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>52.866851946857807</c:v>
+                  <c:v>54.704003939567663</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.218872323757111</c:v>
+                  <c:v>23.070153235054143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.908036944671979</c:v>
+                  <c:v>14.599345888170209</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.0062387847130942</c:v>
+                  <c:v>7.6264969372079809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1766,25 +1766,25 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>17.531621347631578</c:v>
+                  <c:v>17.993346753893537</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.8184779546888024</c:v>
+                  <c:v>9.3527802583721709</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.681724071738351</c:v>
+                  <c:v>12.08022048709045</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.835028572799079</c:v>
+                  <c:v>15.277656440211507</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14.908036944671979</c:v>
+                  <c:v>14.599345888170209</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.218872323757111</c:v>
+                  <c:v>23.070153235054143</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.0062387847130942</c:v>
+                  <c:v>7.6264969372079809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2333,11 +2333,11 @@
       </c>
       <c r="D3" s="27">
         <f>D19</f>
-        <v>52.866851946857807</v>
+        <v>54.704003939567663</v>
       </c>
       <c r="E3" s="27">
         <f>D3-C3</f>
-        <v>2.8668519468578069</v>
+        <v>4.7040039395676629</v>
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -2358,11 +2358,11 @@
       </c>
       <c r="D4" s="27">
         <f>D20</f>
-        <v>24.218872323757111</v>
+        <v>23.070153235054143</v>
       </c>
       <c r="E4" s="27">
         <f>D4-C4</f>
-        <v>-5.7811276762428889</v>
+        <v>-6.9298467649458573</v>
       </c>
       <c r="F4" s="33"/>
       <c r="G4" s="33"/>
@@ -2391,11 +2391,11 @@
       </c>
       <c r="D5" s="27">
         <f>D21</f>
-        <v>14.908036944671979</v>
+        <v>14.599345888170209</v>
       </c>
       <c r="E5" s="27">
         <f>D5-C5</f>
-        <v>-9.1963055328021071E-2</v>
+        <v>-0.40065411182979105</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
@@ -2416,11 +2416,11 @@
       </c>
       <c r="D6" s="27">
         <f>D22</f>
-        <v>8.0062387847130942</v>
+        <v>7.6264969372079809</v>
       </c>
       <c r="E6" s="27">
         <f>D6-C6</f>
-        <v>3.0062387847130942</v>
+        <v>2.6264969372079809</v>
       </c>
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
@@ -2487,11 +2487,11 @@
       </c>
       <c r="D9" s="27">
         <f>C29</f>
-        <v>33.161840930597691</v>
+        <v>32.892193364440118</v>
       </c>
       <c r="E9" s="27">
         <f>D9-C9</f>
-        <v>3.1618409305976911</v>
+        <v>2.8921933644401179</v>
       </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
@@ -2512,11 +2512,11 @@
       </c>
       <c r="D10" s="27">
         <f>C30</f>
-        <v>18.572087410384142</v>
+        <v>17.097067097143984</v>
       </c>
       <c r="E10" s="27">
         <f>D10-C10</f>
-        <v>-1.4279125896158575</v>
+        <v>-2.9029329028560156</v>
       </c>
       <c r="F10" s="33"/>
       <c r="G10" s="33"/>
@@ -2545,11 +2545,11 @@
       </c>
       <c r="D11" s="27">
         <f>C31</f>
-        <v>23.988044691002454</v>
+        <v>22.082881721849194</v>
       </c>
       <c r="E11" s="27">
         <f>D11-C11</f>
-        <v>3.9880446910024538</v>
+        <v>2.0828817218491942</v>
       </c>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -2570,11 +2570,11 @@
       </c>
       <c r="D12" s="27">
         <f>C32</f>
-        <v>24.278026968015713</v>
+        <v>27.927857816566704</v>
       </c>
       <c r="E12" s="27">
         <f>D12-C12</f>
-        <v>-5.7219730319842874</v>
+        <v>-2.0721421834332965</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="33"/>
@@ -2724,11 +2724,11 @@
       </c>
       <c r="C19" s="27">
         <f>Holdings!C43</f>
-        <v>13206413.99</v>
+        <v>14345774.84</v>
       </c>
       <c r="D19" s="27">
         <f>SUM(Holdings!D35:'Holdings'!D38)</f>
-        <v>52.866851946857807</v>
+        <v>54.704003939567663</v>
       </c>
       <c r="E19" s="42">
         <v>9.5000000000000001E-2</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D20" s="40">
         <f>Holdings!D40</f>
-        <v>24.218872323757111</v>
+        <v>23.070153235054143</v>
       </c>
       <c r="E20" s="41">
         <v>0.14499999999999999</v>
@@ -2774,11 +2774,11 @@
       </c>
       <c r="C21" s="27">
         <f>Holdings!C39</f>
-        <v>3724105</v>
+        <v>3828585</v>
       </c>
       <c r="D21" s="27">
         <f>Holdings!D39</f>
-        <v>14.908036944671979</v>
+        <v>14.599345888170209</v>
       </c>
       <c r="E21" s="42">
         <v>1.0500000000000001E-2</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="D22" s="40">
         <f>Holdings!D41</f>
-        <v>8.0062387847130942</v>
+        <v>7.6264969372079809</v>
       </c>
       <c r="E22" s="41">
         <v>0.105</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C29" s="40">
         <f>Holdings!C35/C19*100</f>
-        <v>33.161840930597691</v>
+        <v>32.892193364440118</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="37"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C30" s="27">
         <f>Holdings!C36/C19*100</f>
-        <v>18.572087410384142</v>
+        <v>17.097067097143984</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="C31" s="40">
         <f>Holdings!C37/C19*100</f>
-        <v>23.988044691002454</v>
+        <v>22.082881721849194</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="37"/>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="C32" s="27">
         <f>Holdings!C38/C19*100</f>
-        <v>24.278026968015713</v>
+        <v>27.927857816566704</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -3335,11 +3335,11 @@
         <v>5</v>
       </c>
       <c r="D4" s="9">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="E4" s="22">
         <f>H4/(SUM(H4:H7))*100</f>
-        <v>24.920709945678606</v>
+        <v>22.449265042469865</v>
       </c>
       <c r="F4" s="9">
         <v>32.1</v>
@@ -3350,15 +3350,15 @@
       </c>
       <c r="H4" s="9">
         <f>D4*F4</f>
-        <v>1091400</v>
+        <v>1059300</v>
       </c>
       <c r="I4" s="10">
         <f>D4*G4</f>
-        <v>1159400</v>
+        <v>1125300</v>
       </c>
       <c r="J4" s="10">
         <f>I4-H4</f>
-        <v>68000</v>
+        <v>66000</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
@@ -3377,11 +3377,11 @@
         <v>5</v>
       </c>
       <c r="D5" s="11">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E5" s="22">
         <f>H5/(SUM(H4:H7))*100</f>
-        <v>16.954028893775302</v>
+        <v>23.603199226895885</v>
       </c>
       <c r="F5" s="11">
         <v>74.25</v>
@@ -3392,15 +3392,15 @@
       </c>
       <c r="H5" s="11">
         <f>D5*F5</f>
-        <v>742500</v>
+        <v>1113750</v>
       </c>
       <c r="I5" s="10">
         <f>D5*G5</f>
-        <v>762500</v>
+        <v>1143750</v>
       </c>
       <c r="J5" s="10">
         <f>I5-H5</f>
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E6" s="22">
         <f>H6/(SUM(H4:H7))*100</f>
-        <v>28.958851373105087</v>
+        <v>26.877447739179082</v>
       </c>
       <c r="F6" s="9">
         <v>66.75</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="E7" s="22">
         <f>H7/(SUM(H4:H7))*100</f>
-        <v>29.166409787441005</v>
+        <v>27.070087991455168</v>
       </c>
       <c r="F7" s="11">
         <v>87.25</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E18" s="22">
         <f>H18/(SUM(H18:H20))*100</f>
-        <v>28.545624114475547</v>
+        <v>22.844213191690358</v>
       </c>
       <c r="F18" s="9">
         <v>9.18</v>
@@ -3821,11 +3821,11 @@
         <v>3.33</v>
       </c>
       <c r="D19" s="12">
-        <v>39705</v>
+        <v>91836</v>
       </c>
       <c r="E19" s="22">
         <f>H19/(SUM(H18:H20))*100</f>
-        <v>19.008825478496068</v>
+        <v>35.185174092010627</v>
       </c>
       <c r="F19" s="12">
         <v>15.35</v>
@@ -3836,15 +3836,15 @@
       </c>
       <c r="H19" s="12">
         <f>D19*F19</f>
-        <v>609471.75</v>
+        <v>1409682.5999999999</v>
       </c>
       <c r="I19" s="14">
         <f>D19*G19</f>
-        <v>688881.75</v>
+        <v>1593354.6</v>
       </c>
       <c r="J19" s="10">
         <f>I19-H19</f>
-        <v>79410</v>
+        <v>183672.00000000023</v>
       </c>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="E20" s="22">
         <f t="shared" ref="E20" si="0">H20/(SUM(H18:H20))*100</f>
-        <v>52.445550407028385</v>
+        <v>41.970612716299023</v>
       </c>
       <c r="F20" s="9">
         <v>55.5</v>
@@ -3941,11 +3941,11 @@
         <v>10</v>
       </c>
       <c r="D23" s="9">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E23" s="22">
         <f>H23/(SUM(H23:H24))*100</f>
-        <v>70.137657235765374</v>
+        <v>70.952584309869053</v>
       </c>
       <c r="F23" s="9">
         <v>52240</v>
@@ -3956,15 +3956,15 @@
       </c>
       <c r="H23" s="9">
         <f>D23*F23</f>
-        <v>2612000</v>
+        <v>2716480</v>
       </c>
       <c r="I23" s="10">
         <f>D23*G23</f>
-        <v>2612100</v>
+        <v>2716584</v>
       </c>
       <c r="J23" s="10">
         <f>I23-H23</f>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="E24" s="22">
         <f>H24/(SUM(H23:H24))*100</f>
-        <v>29.862342764234629</v>
+        <v>29.047415690130951</v>
       </c>
       <c r="F24" s="12">
         <v>11465</v>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="C35" s="25">
         <f>SUM(H4:H7)</f>
-        <v>4379490</v>
+        <v>4718640</v>
       </c>
       <c r="D35" s="25">
         <f>C35/C45*100</f>
-        <v>17.531621347631578</v>
+        <v>17.993346753893537</v>
       </c>
       <c r="E35" s="25"/>
       <c r="F35" s="18"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D36" s="25">
         <f>C36/C45*100</f>
-        <v>9.8184779546888024</v>
+        <v>9.3527802583721709</v>
       </c>
       <c r="E36" s="26"/>
       <c r="F36" s="19"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D37" s="25">
         <f>C37/C45*100</f>
-        <v>12.681724071738351</v>
+        <v>12.08022048709045</v>
       </c>
       <c r="E37" s="25"/>
       <c r="F37" s="18"/>
@@ -4318,11 +4318,11 @@
       </c>
       <c r="C38" s="26">
         <f>SUM(H18:H20)</f>
-        <v>3206256.75</v>
+        <v>4006467.5999999996</v>
       </c>
       <c r="D38" s="25">
         <f>C38/C45*100</f>
-        <v>12.835028572799079</v>
+        <v>15.277656440211507</v>
       </c>
       <c r="E38" s="26"/>
       <c r="F38" s="19"/>
@@ -4343,11 +4343,11 @@
       </c>
       <c r="C39" s="25">
         <f>SUM(H23:H24)</f>
-        <v>3724105</v>
+        <v>3828585</v>
       </c>
       <c r="D39" s="25">
         <f>C39/C45*100</f>
-        <v>14.908036944671979</v>
+        <v>14.599345888170209</v>
       </c>
       <c r="E39" s="25"/>
       <c r="F39" s="18"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D40" s="25">
         <f>C40/C45*100</f>
-        <v>24.218872323757111</v>
+        <v>23.070153235054143</v>
       </c>
       <c r="E40" s="26"/>
       <c r="F40" s="19"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D41" s="25">
         <f>C41/C45*100</f>
-        <v>8.0062387847130942</v>
+        <v>7.6264969372079809</v>
       </c>
       <c r="E41" s="25"/>
       <c r="F41" s="18"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C43" s="36">
         <f>SUM(C35:C38)</f>
-        <v>13206413.99</v>
+        <v>14345774.84</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="25"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C45" s="25">
         <f>SUM(C35:C41)</f>
-        <v>24980518.990000002</v>
+        <v>26224359.84</v>
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="28"/>
@@ -4577,7 +4577,7 @@
       <c r="C2" s="14"/>
       <c r="D2" s="14">
         <f>Holdings!D4</f>
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="E2" s="14"/>
     </row>
@@ -4589,7 +4589,7 @@
       <c r="C3" s="14"/>
       <c r="D3" s="14">
         <f>Holdings!D5</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E3" s="14"/>
     </row>
@@ -4685,7 +4685,7 @@
       <c r="C11" s="14"/>
       <c r="D11" s="14">
         <f>Holdings!D19</f>
-        <v>39705</v>
+        <v>91836</v>
       </c>
       <c r="E11" s="14"/>
     </row>
@@ -4709,7 +4709,7 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14">
         <f>Holdings!D23</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" s="14"/>
     </row>
